--- a/修改记录.xlsx
+++ b/修改记录.xlsx
@@ -4,32 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17760"/>
+    <workbookView windowWidth="21000" windowHeight="8315"/>
   </bookViews>
   <sheets>
     <sheet name="YG 108H" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
   <si>
     <t>FW release history</t>
   </si>
@@ -69,16 +56,154 @@
     <t>1.修改长按电源键不关机的问题
 2.进入关机流程时先关闭指示灯，在做定时器，定时器里面关闭喇叭，power_en</t>
   </si>
+  <si>
+    <t>碰撞开机录紧急视频途中接acc不关机，接着录循环视频。</t>
+  </si>
+  <si>
+    <t>1，ios恢复出厂声音播放不全。
+2，修改概率性不升级。</t>
+  </si>
+  <si>
+    <t>1，iOS：在APP设置界面进入缩时录影后，退出缩时录影，进入正常录像后，短按恢复默认键/WIFI 开关/电源键无作用；
+2，紧急录像加锁后，切换录制下一段视频，此时录像状态指示灯还是加锁状态，应是正常录像状态；
+3，WiFi后缀为6C11这台机器，恢复出厂设置，开机录像自动加锁（这台机器的灵敏度较高）；
+4，进入缩时录影模式后，短按功能键还有作用（如WiFi、电源键、暂停开始录像/开关机）；</t>
+  </si>
+  <si>
+    <t>1，安卓、iOS：1080P+1分钟，录出来的视频多13秒，视频播放到最后异常慢；
+2，安卓、iOS：2K+2分钟，录出来的视频长度是2分25秒/视频回放卡顿；
+3，安卓APP端回放视频无声音；
+4，降压线供电：停车监控设置为开，长按电源键关机后，碰撞设备开机，录完停车监控紧急录像会关机/此时ACC重新熄火点火不开机
+5，停车碰撞紧急录像途中ACC点火，此时录完停车紧急视频会自动关机；
+6，紧急录像加锁后，切换录制下一段视频，此时录像状态指示灯还是加锁状态，应是正常录像状态；
+7，iOS/安卓-WiFi后缀为6C11/863C这两台机器将WiFi密码改成qqqqqqqq,设备重启机后，
+找不到WiFi名称,此时短按WiFi键也无作用，只有按键音；
+8，WiFi名称为863C这台机器，将WiFi名称后缀改为11111，将WiFi改成88889999，设备重启机后，找不到WiFi；
+9，2台机器，app端恢复出厂设置后，手机端找不到设备端的WiFi；
+10，iOS：在APP设置界面进入缩时录影后，退出缩时录影，进入正常录像后，短按恢复默认键/WIFI 开关/电源键无作用；
+11，APP端确认恢复出厂设置后，设备端的语音为播报全还有一点异常声；
+12，进入缩时录影模式后，短按功能键还有作用（如WiFi、电源键、暂停开始录像/开关机）；</t>
+  </si>
+  <si>
+    <t>1，停车监控和重力感应灵敏度都太灵敏了；
+2，iOS、安卓，就几个文件，全部删除或只删除两个文件，返回到直播预览再进入到回放界面文件未全部删除掉；</t>
+  </si>
+  <si>
+    <t>1，iOS：APP设置界面断开ACC，设备进入缩时录影后，APP端未退出设置界面（APP端未检测到WiFi关闭）。需要很久才能检测到，参考安卓快速检测；
+2，断开ACC，进入缩时录影模式后，WiFi灯未关闭；
+3，删除全部文件在文件夹界面/设置界面：结束APP进程，再进入到直播预览不会自动录像；
+4，WiFi设置为关，停车监控碰撞开机，紧急录像途中ACC点火，此时在短按WiFi键无法打开WiFi；</t>
+  </si>
+  <si>
+    <t>1，停车碰撞紧急录像途中ACC点火，不关机，自动切换为正常循环录像；
+2，APP端确认恢复出厂设置，设备端的语音播报不全，有一点异常声；
+3，APP设置界面断开ACC，设备进入缩时录影后，APP端未退出设置界面；
+4，碰撞开机录紧急视频途中接acc不关机，接着录循环视频；</t>
+  </si>
+  <si>
+    <t>1，停车监控碰撞开机后，ACC点火，链接WiFii打开APP，进入设置在进入回放界面设备重启；
+2，安卓前后录直播预览界面无经纬度信息；</t>
+  </si>
+  <si>
+    <t>1，车充供电：1分钟开关机测试，PC端查看，前后录视频长度不一致，实际前录视频长度有53秒，但pc显示前录文件16秒，后录文件53秒。
+2，车充供电，1分钟开关机测试，视频长度有低于51秒现象。
+3，车充供电：1分钟开关机测试：视频长度有大于一分钟现象。
+4，降压线供电：1分钟开关机测试，前录有0秒文件和视频长度只有39秒。
+5，降压线供电：1分钟开关机老化，前后路视频只有2秒。
+6，降压线供电：1分钟开关机，个别视频长度有1分钟（1分钟开关机测试视频长度不一致）。</t>
+  </si>
+  <si>
+    <t>iOS/安卓：格完卡，紧急录像途中进入紧急录像文件夹里无文件；</t>
+  </si>
+  <si>
+    <t>1，降压线供电，1分钟开关机老化测试前后录有1秒文件；
+2，降压线，1分钟开关机老化测试，视频长度不一致，有的是1分钟，有的是45秒，有的是54秒；</t>
+  </si>
+  <si>
+    <t>1，GPS未定位，上电开后观察，GPS指示灯会亮一下绿色在亮红色；
+2，设置、记录仪文件夹界面拔掉SD卡再插上SD卡，会自动录像；
+3，1.2.3分钟循环前路视频文件在APP端回放多一秒（PC端查看1.2分钟的有多一秒的现象，3分钟的没有）；
+4，iOS：前录直播预览经纬度显示看不清楚，把经纬度的字体调一下（经纬度与系统时间有点重叠）；</t>
+  </si>
+  <si>
+    <t>1，GPS掉线后，直播预览的经纬度信息还在；
+2，1.2.3分钟循环前路视频文件在APP端回放多一秒（PC端查看1.2分钟的有多一秒的现象，3分钟的没有）；</t>
+  </si>
+  <si>
+    <t>WiF后缀为862B关机铃声结束后会有点异常声音噗（开机前也有比较轻微）；</t>
+  </si>
+  <si>
+    <t>8189 WiFi单跑WiFi模块和全功能做对比，经验证速率也没有提升。</t>
+  </si>
+  <si>
+    <t>连接acc时app显示停车监控，缩时录影菜单，断开app时隐藏。</t>
+  </si>
+  <si>
+    <t>把wifi发射功率改大，验证速率没有提升。</t>
+  </si>
+  <si>
+    <t>发送功率改小验证对WiFi速率的提升；</t>
+  </si>
+  <si>
+    <t>优化应用层代码，把car_demo和对cpu的占用降到22%一下。</t>
+  </si>
+  <si>
+    <t>排查应用层WiFi线程部分报错对WiFi速率的影响。</t>
+  </si>
+  <si>
+    <t>修改减小car_demo对cpu占用后40M带宽未生效问题。</t>
+  </si>
+  <si>
+    <t>添加扬声器音量菜单，音量默认设置为低；</t>
+  </si>
+  <si>
+    <t>优化开机五分钟不连app自动关闭WiFi，添加五分钟内有手动操作不关闭WiFi逻辑。</t>
+  </si>
+  <si>
+    <t>1，ts流解决安卓回放无声音。
+2，添加WiFi打开提示音。
+3，优化关机时短促的“噗”声。</t>
+  </si>
+  <si>
+    <t>wifi打开语音改为英文。</t>
+  </si>
+  <si>
+    <t>前摄在线预览的时间水印，移到下方一点，跟后摄水印一样的位置。</t>
+  </si>
+  <si>
+    <t>调整时间水印和gps水印排版，整体下移。</t>
+  </si>
+  <si>
+    <t>1，把gps星值保存到卡里。 
+2，调整时间水印和gps水印排版，整体下移。 3，去新高诚协助优化gps定位慢问题。</t>
+  </si>
+  <si>
+    <t>修改x2v60星值保存出错问题。</t>
+  </si>
+  <si>
+    <t>gps星值写卡添加时间戳。</t>
+  </si>
+  <si>
+    <t>添加子码流水印切换逻辑。
+定到位正常显示gps和时间水印，定不到位只显示时间水印，并把时间水印下移。</t>
+  </si>
+  <si>
+    <t>验证wifi工作电压对速率的影响，
+用示波器测量8189WiFi工作电压，峰-峰值在120mv以内，平均电压在3.46v。根据高盛达反馈8189工作电压在3.3±0.3V，该电压可以达到。</t>
+  </si>
+  <si>
+    <t>用示波器测量8189WiFi工作电压，峰-峰值在120mv以内，平均电压在3.46v。</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -127,6 +252,125 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="52"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color indexed="56"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color indexed="56"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="20"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="56"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="23"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="62"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="52"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="63"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="60"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color indexed="56"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -134,125 +378,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color indexed="56"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color indexed="23"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color indexed="56"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color indexed="56"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="56"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="62"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="63"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="52"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="52"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="20"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="60"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="24">
     <fill>
@@ -269,19 +394,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor indexed="51"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="11"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="29"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="45"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="20"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="26"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="47"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="22"/>
+        <fgColor indexed="53"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="44"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="46"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="62"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -293,97 +484,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="42"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="45"/>
+        <fgColor indexed="31"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="57"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="27"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="43"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="62"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="31"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="44"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="30"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="10"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="29"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="57"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="11"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="20"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="46"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="27"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="53"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="51"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -481,6 +606,50 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="23"/>
+      </left>
+      <right style="thin">
+        <color indexed="23"/>
+      </right>
+      <top style="thin">
+        <color indexed="23"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="62"/>
+      </top>
+      <bottom style="double">
+        <color indexed="62"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="30"/>
       </bottom>
       <diagonal/>
     </border>
@@ -503,41 +672,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thick">
-        <color indexed="62"/>
+      <bottom style="double">
+        <color indexed="52"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="30"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="23"/>
+      <left style="double">
+        <color indexed="63"/>
       </left>
-      <right style="thin">
-        <color indexed="23"/>
+      <right style="double">
+        <color indexed="63"/>
       </right>
-      <top style="thin">
-        <color indexed="23"/>
+      <top style="double">
+        <color indexed="63"/>
       </top>
-      <bottom style="thin">
-        <color indexed="23"/>
+      <bottom style="double">
+        <color indexed="63"/>
       </bottom>
       <diagonal/>
     </border>
@@ -557,36 +708,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color indexed="63"/>
-      </left>
-      <right style="double">
-        <color indexed="63"/>
-      </right>
-      <top style="double">
-        <color indexed="63"/>
-      </top>
-      <bottom style="double">
-        <color indexed="63"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color indexed="52"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="62"/>
-      </top>
-      <bottom style="double">
+      <bottom style="thick">
         <color indexed="62"/>
       </bottom>
       <diagonal/>
@@ -594,138 +719,138 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="13">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -776,52 +901,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1129,8 +1254,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="41.25" style="1"/>
     <col min="2" max="2" width="4.5" style="2"/>
@@ -1206,7 +1331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" ht="22.5" spans="1:3">
+    <row r="7" ht="41" customHeight="1" spans="1:3">
       <c r="A7" s="10">
         <v>20241203</v>
       </c>
@@ -1214,7 +1339,278 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" ht="38" customHeight="1"/>
+    <row r="8" ht="17" customHeight="1" spans="1:3">
+      <c r="A8" s="10">
+        <v>20241209</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1" spans="1:3">
+      <c r="A9" s="10">
+        <v>20241210</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1" spans="1:3">
+      <c r="A10" s="10">
+        <v>20241215</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" ht="55" customHeight="1" spans="1:3">
+      <c r="A11" s="10">
+        <v>20241216</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" ht="152" customHeight="1" spans="1:3">
+      <c r="A12" s="10">
+        <v>20241217</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:3">
+      <c r="A13" s="10">
+        <v>20241218</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" ht="63" customHeight="1" spans="1:3">
+      <c r="A14" s="10">
+        <v>20241219</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" ht="53" customHeight="1" spans="1:3">
+      <c r="A15" s="10">
+        <v>20241223</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:3">
+      <c r="A16" s="10">
+        <v>20241225</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" ht="84" customHeight="1" spans="1:3">
+      <c r="A17" s="10">
+        <v>20241228</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="10">
+        <v>20241231</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" ht="27" customHeight="1" spans="1:3">
+      <c r="A19" s="10">
+        <v>20250102</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" ht="51" customHeight="1" spans="1:3">
+      <c r="A20" s="10">
+        <v>20250106</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" ht="27" customHeight="1" spans="1:3">
+      <c r="A21" s="10">
+        <v>20250107</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="10">
+        <v>20250108</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="10">
+        <v>20250111</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="10">
+        <v>20250113</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="10">
+        <v>20250114</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="10">
+        <v>20250115</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="10">
+        <v>20250116</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="10">
+        <v>20250117</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="10">
+        <v>20250118</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="10">
+        <v>20250121</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="10">
+        <v>20250205</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" ht="38" customHeight="1" spans="1:3">
+      <c r="A32" s="10">
+        <v>20250206</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="10">
+        <v>20250207</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="10">
+        <v>20250208</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="10">
+        <v>20250220</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1" spans="1:3">
+      <c r="A36" s="10">
+        <v>20250221</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="10">
+        <v>20250227</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="10">
+        <v>20250307</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1" spans="1:3">
+      <c r="A39" s="10">
+        <v>20250314</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" ht="38" customHeight="1" spans="1:3">
+      <c r="A40" s="10">
+        <v>20250324</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="10">
+        <v>20250328</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
@@ -1229,7 +1625,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="30066" verticalDpi="26478"/>
@@ -1241,7 +1637,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="30066" verticalDpi="26478"/>

--- a/修改记录.xlsx
+++ b/修改记录.xlsx
@@ -4,19 +4,32 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="8315"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="YG 108H" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>FW release history</t>
   </si>
@@ -194,16 +207,21 @@
   <si>
     <t>用示波器测量8189WiFi工作电压，峰-峰值在120mv以内，平均电压在3.46v。</t>
   </si>
+  <si>
+    <t>1，缩时录影改为帧率和时长都打开才进入缩时录影，关闭其一断开acc则关机。其中帧率默认值改为1帧/s。
+2，修改gps上下掉线切换时时间水印和gps水印会重叠。
+3，前路4k和2k水印坐标下移。</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -252,8 +270,72 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color indexed="8"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color indexed="56"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="23"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color indexed="56"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color indexed="56"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="56"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="62"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="63"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -266,14 +348,14 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color indexed="56"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color indexed="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="52"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -285,9 +367,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color indexed="56"/>
+      <sz val="11"/>
+      <color indexed="17"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -298,85 +379,22 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color indexed="56"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color indexed="23"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="62"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="52"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
+      <color indexed="60"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color indexed="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color indexed="63"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="60"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color indexed="56"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="24">
@@ -394,121 +412,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor indexed="26"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="55"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="45"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="62"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="31"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="44"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="29"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="57"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="11"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="20"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="46"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="27"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="53"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="51"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="47"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="22"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="11"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="42"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="29"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="45"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="20"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="26"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="53"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="44"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="46"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="10"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="62"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="55"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="31"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="30"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="57"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="27"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="43"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -606,50 +624,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="23"/>
-      </left>
-      <right style="thin">
-        <color indexed="23"/>
-      </right>
-      <top style="thin">
-        <color indexed="23"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="23"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="62"/>
-      </top>
-      <bottom style="double">
-        <color indexed="62"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="30"/>
       </bottom>
       <diagonal/>
     </border>
@@ -672,8 +646,56 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color indexed="52"/>
+      <bottom style="thick">
+        <color indexed="62"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="30"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="23"/>
+      </left>
+      <right style="thin">
+        <color indexed="23"/>
+      </right>
+      <top style="thin">
+        <color indexed="23"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="63"/>
+      </left>
+      <right style="thin">
+        <color indexed="63"/>
+      </right>
+      <top style="thin">
+        <color indexed="63"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="63"/>
       </bottom>
       <diagonal/>
     </border>
@@ -693,25 +715,21 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="63"/>
-      </left>
-      <right style="thin">
-        <color indexed="63"/>
-      </right>
-      <top style="thin">
-        <color indexed="63"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="63"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="52"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thick">
+      <top style="thin">
+        <color indexed="62"/>
+      </top>
+      <bottom style="double">
         <color indexed="62"/>
       </bottom>
       <diagonal/>
@@ -719,138 +737,138 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="15">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="14">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="13">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -901,52 +919,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1254,8 +1272,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="5"/>
+  <dimension ref="A1:F42"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="41.25" style="1"/>
     <col min="2" max="2" width="4.5" style="2"/>
@@ -1611,6 +1629,14 @@
         <v>43</v>
       </c>
     </row>
+    <row r="42" ht="40" customHeight="1" spans="1:3">
+      <c r="A42" s="10">
+        <v>20250408</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
@@ -1625,7 +1651,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="30066" verticalDpi="26478"/>
@@ -1637,7 +1663,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="30066" verticalDpi="26478"/>
